--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -446,7 +446,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Organization.extension:prefectureNo</t>
@@ -804,7 +804,7 @@
     <t>福祉医療施設を区別するため医療機関コード（１０桁）を格納するためのIdentifier/Slicing定義。</t>
   </si>
   <si>
-    <t xml:space="preserve">systemはFixed Valueの```http://jpfhir.jp/fhir/core/IdSystem/insurance-medical-institution-no```を使用する。  
+    <t xml:space="preserve">systemはFixed Valueの```http://jpfhir.jp/fhir/core/IdSystem/medicalInstitutionCode```を使用する。  
 value : ```医療機関コード（１０桁）```を使用する。  
 医療機関コード（１０桁）の詳細はOrganizationプロファイルの医療機関コード１０桁の説明を参照すること。 </t>
   </si>
@@ -827,7 +827,7 @@
     <t>Organization.identifier:medicalInstitutionCode.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/insurance-medical-institution-no</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/medicalInstitutionCode</t>
   </si>
   <si>
     <t>Organization.identifier:medicalInstitutionCode.value</t>
@@ -6501,7 +6501,7 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>240</v>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
@@ -6501,7 +6501,7 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>240</v>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
@@ -804,7 +804,7 @@
     <t>福祉医療施設を区別するため医療機関コード（１０桁）を格納するためのIdentifier/Slicing定義。</t>
   </si>
   <si>
-    <t xml:space="preserve">systemはFixed Valueの```http://jpfhir.jp/fhir/core/IdSystem/medicalInstitutionCode```を使用する。  
+    <t xml:space="preserve">systemはFixed Valueの```http://jpfhir.jp/fhir/core/IdSystem/insurance-medical-institution-no```を使用する。  
 value : ```医療機関コード（１０桁）```を使用する。  
 医療機関コード（１０桁）の詳細はOrganizationプロファイルの医療機関コード１０桁の説明を参照すること。 </t>
   </si>
@@ -827,7 +827,7 @@
     <t>Organization.identifier:medicalInstitutionCode.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/medicalInstitutionCode</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/insurance-medical-institution-no</t>
   </si>
   <si>
     <t>Organization.identifier:medicalInstitutionCode.value</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
